--- a/docs/tutorial-assets/workbooks/02_PyroApp_DAT_Inspection_and_Editing_Ca-Zn-O.xlsx
+++ b/docs/tutorial-assets/workbooks/02_PyroApp_DAT_Inspection_and_Editing_Ca-Zn-O.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_WORK\Code\Rust\pyroapp-docs\docs\tutorial-assets\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FCDBED-7C95-4CF9-ADEA-07D2880C9D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE87EDF-874A-4D4A-94E0-D37585C9DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>PyroApp Example 02 — DAT Inspection and Editing (Ca-Zn-O)</t>
   </si>
   <si>
-    <t>Browse an open DAT, read compound/constituent parameters, inspect interactions and use a gated SET operation.</t>
+    <t>Browse a disposable working DAT, read compound/constituent parameters, inspect interactions and use a gated SET operation.</t>
   </si>
   <si>
     <t>Before you calculate</t>
@@ -74,7 +74,7 @@
     <t>1. Install/load PyroApp in desktop Excel.</t>
   </si>
   <si>
-    <t>2. Download Ca-Zn-O.dat and place it beside this workbook.</t>
+    <t>2. Download Ca-Zn-O_editing_working.dat and place it beside this workbook.</t>
   </si>
   <si>
     <t>3. Blue cells are inputs; black cells are formulas; purple cells are controls.</t>
@@ -86,7 +86,7 @@
     <t>Datafile</t>
   </si>
   <si>
-    <t>Ca-Zn-O.dat</t>
+    <t>Ca-Zn-O_editing_working.dat</t>
   </si>
   <si>
     <t>Download DAT</t>
@@ -206,7 +206,7 @@
     <t>Gated SET example</t>
   </si>
   <si>
-    <t>SET modifies the DAT file. Leave Enable SET = FALSE until you intentionally want to write the Proposed value. Keep an untouched reference DAT.</t>
+    <t>This workbook opens Ca-Zn-O_editing_working.dat. Ca-Zn-O.dat is the baseline reference. SET modifies only the working DAT, and Enable SET is FALSE by default so opening or recalculating this workbook cannot write either file.</t>
   </si>
   <si>
     <t>Value index</t>
@@ -659,7 +659,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1015,7 +1015,8 @@
   <cols>
     <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="18" customWidth="1"/>
+    <col min="3" max="4" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1044,8 +1045,8 @@
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_H298(Start!$B$10,$B$4)</f>
+      <c r="B6" s="1" cm="1">
+        <f t="array" ref="B6">_xll.XLL_CA_GET_COMPOUND_H298(Start!$B$10,$B$4)</f>
         <v>0</v>
       </c>
     </row>
@@ -1053,8 +1054,8 @@
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_S298(Start!$B$10,$B$4)</f>
+      <c r="B7" s="1" cm="1">
+        <f t="array" ref="B7">_xll.XLL_CA_GET_COMPOUND_S298(Start!$B$10,$B$4)</f>
         <v>0</v>
       </c>
     </row>
@@ -1062,8 +1063,8 @@
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_WEIGHTS(Start!$B$10,$B$4)</f>
+      <c r="B8" s="1" cm="1">
+        <f t="array" ref="B8">_xll.XLL_CA_GET_COMPOUND_WEIGHTS(Start!$B$10,$B$4)</f>
         <v>56.077400000000004</v>
       </c>
     </row>
@@ -1071,17 +1072,23 @@
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_STOICHIOMETRY(Start!$B$10,$B$4)</f>
+      <c r="B9" s="1" cm="1">
+        <f t="array" ref="B9:D9">_xll.XLL_CA_GET_COMPOUND_STOICHIOMETRY(Start!$B$10,$B$4)</f>
         <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_RANGE_COUNT(Start!$B$10,$B$4)</f>
+      <c r="B10" s="1" cm="1">
+        <f t="array" ref="B10">_xll.XLL_CA_GET_COMPOUND_RANGE_COUNT(Start!$B$10,$B$4)</f>
         <v>1</v>
       </c>
     </row>
@@ -1089,8 +1096,8 @@
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_TUPPER(Start!$B$10,$B$4,1)</f>
+      <c r="B11" s="1" cm="1">
+        <f t="array" ref="B11">_xll.XLL_CA_GET_COMPOUND_TUPPER(Start!$B$10,$B$4,1)</f>
         <v>6001</v>
       </c>
     </row>
@@ -1098,8 +1105,8 @@
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1">
-        <f>_xll.XLL_CA_GET_COMPOUND_CP(Start!$B$10,$B$4,1,1)</f>
+      <c r="B12" s="1" cm="1">
+        <f t="array" ref="B12">_xll.XLL_CA_GET_COMPOUND_CP(Start!$B$10,$B$4,1,1)</f>
         <v>0</v>
       </c>
     </row>
@@ -1118,7 +1125,8 @@
   <cols>
     <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="18" customWidth="1"/>
+    <col min="3" max="4" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1155,8 +1163,8 @@
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_H298(Start!$B$10,$B$4,$B$5)</f>
+      <c r="B7" s="1" cm="1">
+        <f t="array" ref="B7">_xll.XLL_CA_GET_CONSTITUENT_H298(Start!$B$10,$B$4,$B$5)</f>
         <v>0</v>
       </c>
     </row>
@@ -1164,8 +1172,8 @@
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_S298(Start!$B$10,$B$4,$B$5)</f>
+      <c r="B8" s="1" cm="1">
+        <f t="array" ref="B8">_xll.XLL_CA_GET_CONSTITUENT_S298(Start!$B$10,$B$4,$B$5)</f>
         <v>0</v>
       </c>
     </row>
@@ -1173,8 +1181,8 @@
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_WEIGHTS(Start!$B$10,$B$4,$B$5)</f>
+      <c r="B9" s="1" cm="1">
+        <f t="array" ref="B9">_xll.XLL_CA_GET_CONSTITUENT_WEIGHTS(Start!$B$10,$B$4,$B$5)</f>
         <v>56.077400000000004</v>
       </c>
     </row>
@@ -1182,17 +1190,23 @@
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_STOICHIOMETRY(Start!$B$10,$B$4,$B$5)</f>
+      <c r="B10" s="1" cm="1">
+        <f t="array" ref="B10:D10">_xll.XLL_CA_GET_CONSTITUENT_STOICHIOMETRY(Start!$B$10,$B$4,$B$5)</f>
         <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_RANGE_COUNT(Start!$B$10,$B$4,$B$5)</f>
+      <c r="B11" s="1" cm="1">
+        <f t="array" ref="B11">_xll.XLL_CA_GET_CONSTITUENT_RANGE_COUNT(Start!$B$10,$B$4,$B$5)</f>
         <v>2</v>
       </c>
     </row>
@@ -1200,8 +1214,8 @@
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_TUPPER(Start!$B$10,$B$4,$B$5,1)</f>
+      <c r="B12" s="1" cm="1">
+        <f t="array" ref="B12">_xll.XLL_CA_GET_CONSTITUENT_TUPPER(Start!$B$10,$B$4,$B$5,1)</f>
         <v>2845.1599000000001</v>
       </c>
     </row>
@@ -1209,8 +1223,8 @@
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="1">
-        <f>_xll.XLL_CA_GET_CONSTITUENT_CP(Start!$B$10,$B$4,$B$5,1,1)</f>
+      <c r="B13" s="1" cm="1">
+        <f t="array" ref="B13">_xll.XLL_CA_GET_CONSTITUENT_CP(Start!$B$10,$B$4,$B$5,1,1)</f>
         <v>-571766.66</v>
       </c>
     </row>
@@ -1295,8 +1309,8 @@
       <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1">
-        <f>_xll.XLL_CA_GET_INTERACTION_INDICES(Start!$B$10,$B$4,$B$24)</f>
+      <c r="B25" s="1" cm="1">
+        <f t="array" ref="B25">_xll.XLL_CA_GET_INTERACTION_INDICES(Start!$B$10,$B$4,$B$24)</f>
         <v>1</v>
       </c>
     </row>
@@ -1374,7 +1388,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
@@ -1413,8 +1427,8 @@
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="1">
-        <f>_xll.XLL_CA_GET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$8,$B$9,$B$10,$B$13)</f>
+      <c r="B11" s="1" cm="1">
+        <f t="array" ref="B11">_xll.XLL_CA_GET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$8,$B$9,$B$10,$B$13)</f>
         <v>-26652.080000000002</v>
       </c>
     </row>
@@ -1448,7 +1462,7 @@
         <v>54</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>IF($B$14,_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$8,$B$9,$B$10,$B$12,$B$13),"Disabled")</f>
+        <f>IF($B$14,_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$8,$B$9,$B$12,$B$10,$B$13),"Disabled")</f>
         <v>Disabled</v>
       </c>
     </row>
